--- a/wolf/Excel/Effects_特效.xlsx
+++ b/wolf/Excel/Effects_特效.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="23040" windowHeight="9015" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="49">
   <si>
     <t>Int</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>0|0|0|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -1363,7 +1366,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U214"/>
+  <dimension ref="A1:U219"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1491,7 +1494,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>525387</v>
+        <v>556585</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1522,10 +1525,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>501310</v>
+        <v>558271</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -1551,14 +1554,12 @@
       <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
+        <v>565350</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1584,14 +1585,12 @@
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>13</v>
+        <v>567138</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1617,14 +1616,12 @@
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
+        <v>567139</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1650,11 +1647,9 @@
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>526080</v>
+        <v>525387</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -1683,12 +1678,12 @@
       <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>464265</v>
+        <v>501310</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1714,12 +1709,14 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C12" s="4">
-        <v>266517</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>57202</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1745,12 +1742,14 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C13" s="4">
-        <v>266518</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>365194</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1776,12 +1775,14 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C14" s="4">
-        <v>266519</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>28451</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1807,12 +1808,14 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" s="4">
-        <v>266520</v>
+        <v>526080</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1840,10 +1843,10 @@
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="4">
-        <v>266521</v>
+        <v>464265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1871,7 +1874,7 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="4">
-        <v>439411</v>
+        <v>266517</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
@@ -1902,10 +1905,10 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="4">
-        <v>484531</v>
+        <v>266518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1933,10 +1936,10 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="4">
-        <v>144088</v>
+        <v>266519</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1964,10 +1967,10 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>439415</v>
+        <v>266520</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -1995,10 +1998,10 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>20</v>
+        <v>266521</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2026,10 +2029,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>326212</v>
+        <v>439411</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2057,10 +2060,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>326224</v>
+        <v>484531</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2088,10 +2091,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>383667</v>
+        <v>144088</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2119,10 +2122,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>383676</v>
+        <v>439415</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2150,9 +2153,9 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>386040</v>
-      </c>
-      <c r="D26" s="2" t="s">
+        <v>144093</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="4">
@@ -2181,10 +2184,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>394667</v>
+        <v>326212</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2212,10 +2215,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>394678</v>
+        <v>326224</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2241,14 +2244,12 @@
       <c r="A29" s="4">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="4">
+        <v>383667</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C29" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2270,16 +2271,16 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" ht="17.25" spans="1:21">
+    <row r="30" spans="1:21">
       <c r="A30" s="4">
         <v>26</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>24</v>
+      <c r="B30" s="6"/>
+      <c r="C30" s="4">
+        <v>383676</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2305,14 +2306,12 @@
       <c r="A31" s="4">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="4">
+        <v>386040</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C31" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2338,14 +2337,12 @@
       <c r="A32" s="4">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="4">
+        <v>394667</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C32" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -2371,14 +2368,12 @@
       <c r="A33" s="4">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="4">
+        <v>394678</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C33" s="4">
-        <v>220843</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2404,14 +2399,14 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
+      <c r="B34" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C34" s="4">
-        <v>220844</v>
+        <v>220840</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2433,18 +2428,16 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" ht="17.25" spans="1:21">
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="4">
-        <v>220845</v>
+      <c r="B35" s="2"/>
+      <c r="C35" s="7">
+        <v>485354</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2470,14 +2463,14 @@
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>22</v>
+      <c r="B36" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C36" s="4">
-        <v>220846</v>
+        <v>220841</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2504,13 +2497,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C37" s="4">
-        <v>220847</v>
+        <v>220842</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2536,14 +2529,14 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
+      <c r="B38" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220848</v>
+        <v>220843</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -2569,14 +2562,14 @@
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>22</v>
+      <c r="B39" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C39" s="4">
-        <v>220849</v>
+        <v>220844</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2603,13 +2596,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220850</v>
+        <v>220845</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -2635,14 +2628,14 @@
       <c r="A41" s="4">
         <v>37</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
+      <c r="B41" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220851</v>
+        <v>220846</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -2668,14 +2661,14 @@
       <c r="A42" s="4">
         <v>38</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>22</v>
+      <c r="B42" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220041</v>
+        <v>220847</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -2702,13 +2695,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220469</v>
+        <v>220848</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -2734,14 +2727,14 @@
       <c r="A44" s="4">
         <v>40</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>25</v>
+      <c r="B44" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
+        <v>220849</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -2768,13 +2761,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
+        <v>220850</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -2801,13 +2794,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -2833,14 +2826,14 @@
       <c r="A47" s="4">
         <v>43</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>28</v>
+      <c r="B47" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
+        <v>220041</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -2866,12 +2859,14 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C48" s="4">
-        <v>144084</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>220469</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -2897,9 +2892,11 @@
       <c r="A49" s="4">
         <v>45</v>
       </c>
-      <c r="B49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C49" s="4">
-        <v>146786</v>
+        <v>31645</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -2928,12 +2925,14 @@
       <c r="A50" s="4">
         <v>46</v>
       </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C50" s="4">
-        <v>144083</v>
+        <v>4366</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2960,10 +2959,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51" s="4">
-        <v>32240</v>
+        <v>4367</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>9</v>
@@ -2993,10 +2992,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" s="4">
-        <v>59956</v>
+        <v>4368</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>9</v>
@@ -3025,14 +3024,12 @@
       <c r="A53" s="4">
         <v>49</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="4">
-        <v>73402</v>
+        <v>144084</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3058,11 +3055,9 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="4">
-        <v>88762</v>
+        <v>146786</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
@@ -3091,14 +3086,12 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="4">
-        <v>88773</v>
+        <v>144083</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3125,10 +3118,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" s="4">
-        <v>89073</v>
+        <v>32240</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>9</v>
@@ -3158,10 +3151,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C57" s="4">
-        <v>89109</v>
+        <v>59956</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
@@ -3191,10 +3184,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C58" s="4">
-        <v>89111</v>
+        <v>73402</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
@@ -3224,10 +3217,10 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" s="4">
-        <v>89112</v>
+        <v>88762</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>9</v>
@@ -3257,10 +3250,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="4">
-        <v>89122</v>
+        <v>88773</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>9</v>
@@ -3290,10 +3283,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4">
-        <v>113903</v>
+        <v>89073</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
@@ -3323,10 +3316,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C62" s="4">
-        <v>113913</v>
+        <v>89109</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -3356,10 +3349,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4">
-        <v>113907</v>
+        <v>89111</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>9</v>
@@ -3389,10 +3382,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C64" s="4">
-        <v>119917</v>
+        <v>89112</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
@@ -3422,10 +3415,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C65" s="4">
-        <v>130776</v>
+        <v>89122</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>9</v>
@@ -3455,10 +3448,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C66" s="4">
-        <v>141655</v>
+        <v>113903</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
@@ -3488,10 +3481,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C67" s="4">
-        <v>141657</v>
+        <v>113913</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>9</v>
@@ -3521,10 +3514,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C68" s="4">
-        <v>142753</v>
+        <v>113907</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -3554,10 +3547,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C69" s="4">
-        <v>142751</v>
+        <v>119917</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>9</v>
@@ -3587,10 +3580,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C70" s="4">
-        <v>142951</v>
+        <v>130776</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>9</v>
@@ -3620,10 +3613,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C71" s="4">
-        <v>156399</v>
+        <v>141655</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
@@ -3652,9 +3645,11 @@
       <c r="A72" s="4">
         <v>68</v>
       </c>
-      <c r="B72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C72" s="4">
-        <v>157113</v>
+        <v>141657</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>9</v>
@@ -3683,9 +3678,11 @@
       <c r="A73" s="4">
         <v>69</v>
       </c>
-      <c r="B73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C73" s="4">
-        <v>157118</v>
+        <v>142753</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>9</v>
@@ -3714,9 +3711,11 @@
       <c r="A74" s="4">
         <v>70</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C74" s="4">
-        <v>157119</v>
+        <v>142751</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
@@ -3746,10 +3745,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C75" s="4">
-        <v>271322</v>
+        <v>142951</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>9</v>
@@ -3779,10 +3778,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C76" s="4">
-        <v>311092</v>
+        <v>156399</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>9</v>
@@ -3811,11 +3810,9 @@
       <c r="A77" s="4">
         <v>73</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="B77" s="2"/>
       <c r="C77" s="4">
-        <v>318586</v>
+        <v>157113</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
@@ -3846,7 +3843,7 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="4">
-        <v>501294</v>
+        <v>157118</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -3875,11 +3872,9 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="4">
-        <v>127013</v>
+        <v>157119</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>9</v>
@@ -3908,9 +3903,11 @@
       <c r="A80" s="4">
         <v>76</v>
       </c>
-      <c r="B80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C80" s="4">
-        <v>146328</v>
+        <v>271322</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>9</v>
@@ -3939,9 +3936,11 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C81" s="4">
-        <v>146328</v>
+        <v>311092</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>9</v>
@@ -3970,9 +3969,11 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C82" s="4">
-        <v>146753</v>
+        <v>318586</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>9</v>
@@ -4001,11 +4002,9 @@
       <c r="A83" s="4">
         <v>79</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>146754</v>
+        <v>501294</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>9</v>
@@ -4035,10 +4034,10 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C84" s="4">
-        <v>144082</v>
+        <v>127013</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>9</v>
@@ -4067,11 +4066,9 @@
       <c r="A85" s="4">
         <v>81</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="B85" s="2"/>
       <c r="C85" s="4">
-        <v>361275</v>
+        <v>146328</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>9</v>
@@ -4097,11 +4094,19 @@
       <c r="U85" s="2"/>
     </row>
     <row r="86" spans="1:21">
-      <c r="A86" s="2"/>
+      <c r="A86" s="4">
+        <v>82</v>
+      </c>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="C86" s="4">
+        <v>146328</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4120,11 +4125,19 @@
       <c r="U86" s="2"/>
     </row>
     <row r="87" spans="1:21">
-      <c r="A87" s="2"/>
+      <c r="A87" s="4">
+        <v>83</v>
+      </c>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="C87" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4143,11 +4156,21 @@
       <c r="U87" s="2"/>
     </row>
     <row r="88" spans="1:21">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="A88" s="4">
+        <v>84</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4166,11 +4189,21 @@
       <c r="U88" s="2"/>
     </row>
     <row r="89" spans="1:21">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="A89" s="4">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4189,11 +4222,21 @@
       <c r="U89" s="2"/>
     </row>
     <row r="90" spans="1:21">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="A90" s="4">
+        <v>86</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C90" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -7063,6 +7106,121 @@
       <c r="T214" s="2"/>
       <c r="U214" s="2"/>
     </row>
+    <row r="215" spans="1:21">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+      <c r="U215" s="2"/>
+    </row>
+    <row r="216" spans="1:21">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2"/>
+      <c r="R216" s="2"/>
+      <c r="S216" s="2"/>
+      <c r="T216" s="2"/>
+      <c r="U216" s="2"/>
+    </row>
+    <row r="217" spans="1:21">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
+      <c r="R217" s="2"/>
+      <c r="S217" s="2"/>
+      <c r="T217" s="2"/>
+      <c r="U217" s="2"/>
+    </row>
+    <row r="218" spans="1:21">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
+      <c r="R218" s="2"/>
+      <c r="S218" s="2"/>
+      <c r="T218" s="2"/>
+      <c r="U218" s="2"/>
+    </row>
+    <row r="219" spans="1:21">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
+      <c r="R219" s="2"/>
+      <c r="S219" s="2"/>
+      <c r="T219" s="2"/>
+      <c r="U219" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/wolf/Excel/Effects_特效.xlsx
+++ b/wolf/Excel/Effects_特效.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -58,10 +58,10 @@
 2-FeMale</t>
   </si>
   <si>
-    <t>0|0|0|0|0|0|1|1|1</t>
+    <t>0|0|50|0|0|0|0.1|0.1|0.1</t>
   </si>
   <si>
-    <t>0|0|150|0|0|0|1|1|1</t>
+    <t>0|0|0|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>广告牌</t>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>剪纸</t>
+  </si>
+  <si>
+    <t>0|0|150|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U219"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1494,7 +1497,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="4">
-        <v>556585</v>
+        <v>681318</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1525,7 +1528,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>558271</v>
+        <v>687895</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1556,10 +1559,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>565350</v>
+        <v>687897</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1587,10 +1590,10 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>567138</v>
+        <v>687899</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1618,10 +1621,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>567139</v>
+        <v>556585</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1649,10 +1652,10 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>525387</v>
+        <v>674918</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1680,10 +1683,10 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>501310</v>
+        <v>565350</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1709,14 +1712,12 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>567138</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1742,14 +1743,12 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>567139</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1775,14 +1774,12 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>525387</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1808,14 +1805,12 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="4">
-        <v>526080</v>
+        <v>501310</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1841,12 +1836,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C16" s="4">
-        <v>464265</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>57202</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1872,12 +1869,14 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C17" s="4">
-        <v>266517</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>365194</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1903,12 +1902,14 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C18" s="4">
-        <v>266518</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>28451</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1934,12 +1935,14 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="C19" s="4">
-        <v>266519</v>
+        <v>526080</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1967,7 +1970,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>266520</v>
+        <v>464265</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
@@ -1998,7 +2001,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266521</v>
+        <v>266517</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
@@ -2029,10 +2032,10 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>439411</v>
+        <v>266518</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2060,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>484531</v>
+        <v>266519</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2091,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>144088</v>
+        <v>266520</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2122,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>439415</v>
+        <v>266521</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2153,10 +2156,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>21</v>
+        <v>439411</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2184,10 +2187,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>326212</v>
+        <v>484531</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2215,10 +2218,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>326224</v>
+        <v>144088</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2246,10 +2249,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>383667</v>
+        <v>439415</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2277,10 +2280,10 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>383676</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>22</v>
+        <v>144093</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2308,7 +2311,7 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>386040</v>
+        <v>326212</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>22</v>
@@ -2339,7 +2342,7 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>394667</v>
+        <v>326224</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>22</v>
@@ -2370,7 +2373,7 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>394678</v>
+        <v>383667</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -2399,14 +2402,12 @@
       <c r="A34" s="4">
         <v>30</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>220840</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>383676</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -2428,16 +2429,16 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" ht="17.25" spans="1:21">
+    <row r="35" spans="1:21">
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="7">
-        <v>485354</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>25</v>
+      <c r="B35" s="6"/>
+      <c r="C35" s="4">
+        <v>386040</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2463,14 +2464,12 @@
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B36" s="6"/>
       <c r="C36" s="4">
-        <v>220841</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>24</v>
+        <v>394667</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2496,14 +2495,12 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="B37" s="6"/>
       <c r="C37" s="4">
-        <v>220842</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>24</v>
+        <v>394678</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2533,7 +2530,7 @@
         <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220843</v>
+        <v>220840</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>24</v>
@@ -2558,18 +2555,16 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" ht="17.25" spans="1:21">
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="4">
-        <v>220844</v>
+      <c r="B39" s="2"/>
+      <c r="C39" s="7">
+        <v>485354</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2599,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220845</v>
+        <v>220841</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>24</v>
@@ -2628,11 +2623,11 @@
       <c r="A41" s="4">
         <v>37</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220846</v>
+        <v>220842</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>24</v>
@@ -2661,11 +2656,11 @@
       <c r="A42" s="4">
         <v>38</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220847</v>
+        <v>220843</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>24</v>
@@ -2698,7 +2693,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220848</v>
+        <v>220844</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>24</v>
@@ -2727,11 +2722,11 @@
       <c r="A44" s="4">
         <v>40</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>220849</v>
+        <v>220845</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>24</v>
@@ -2760,11 +2755,11 @@
       <c r="A45" s="4">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>220850</v>
+        <v>220846</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>24</v>
@@ -2797,7 +2792,7 @@
         <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>220851</v>
+        <v>220847</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>24</v>
@@ -2826,11 +2821,11 @@
       <c r="A47" s="4">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>220041</v>
+        <v>220848</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>24</v>
@@ -2859,11 +2854,11 @@
       <c r="A48" s="4">
         <v>44</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="4">
-        <v>220469</v>
+        <v>220849</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>24</v>
@@ -2893,13 +2888,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C49" s="4">
-        <v>31645</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>220850</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -2926,13 +2921,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C50" s="4">
-        <v>4366</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>220851</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2958,14 +2953,14 @@
       <c r="A51" s="4">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>28</v>
+      <c r="B51" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C51" s="4">
-        <v>4367</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>220041</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2992,13 +2987,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C52" s="4">
-        <v>4368</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>220469</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3024,12 +3019,14 @@
       <c r="A53" s="4">
         <v>49</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C53" s="4">
-        <v>144084</v>
+        <v>31645</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E53" s="4">
         <v>0</v>
@@ -3055,12 +3052,14 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C54" s="4">
-        <v>146786</v>
+        <v>4366</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3086,12 +3085,14 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C55" s="4">
-        <v>144083</v>
+        <v>4367</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E55" s="4">
         <v>0</v>
@@ -3118,13 +3119,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56" s="4">
-        <v>32240</v>
+        <v>4368</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3150,14 +3151,12 @@
       <c r="A57" s="4">
         <v>53</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="4">
-        <v>59956</v>
+        <v>144084</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3183,14 +3182,12 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="4">
-        <v>73402</v>
+        <v>146786</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
@@ -3216,14 +3213,12 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="4">
-        <v>88762</v>
+        <v>144083</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3250,13 +3245,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C60" s="4">
-        <v>88773</v>
+        <v>32240</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
@@ -3283,13 +3278,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C61" s="4">
-        <v>89073</v>
+        <v>59956</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
@@ -3316,13 +3311,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C62" s="4">
-        <v>89109</v>
+        <v>73402</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
@@ -3349,13 +3344,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C63" s="4">
-        <v>89111</v>
+        <v>88762</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
@@ -3382,13 +3377,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C64" s="4">
-        <v>89112</v>
+        <v>88773</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
@@ -3415,13 +3410,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4">
-        <v>89122</v>
+        <v>89073</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
@@ -3448,13 +3443,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4">
-        <v>113903</v>
+        <v>89109</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -3481,13 +3476,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C67" s="4">
-        <v>113913</v>
+        <v>89111</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
@@ -3514,13 +3509,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C68" s="4">
-        <v>113907</v>
+        <v>89112</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
@@ -3547,13 +3542,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C69" s="4">
-        <v>119917</v>
+        <v>89122</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
@@ -3580,13 +3575,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C70" s="4">
-        <v>130776</v>
+        <v>113903</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
@@ -3613,13 +3608,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4">
-        <v>141655</v>
+        <v>113913</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
@@ -3646,13 +3641,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C72" s="4">
-        <v>141657</v>
+        <v>113907</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
@@ -3679,13 +3674,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C73" s="4">
-        <v>142753</v>
+        <v>119917</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
@@ -3712,13 +3707,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C74" s="4">
-        <v>142751</v>
+        <v>130776</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
@@ -3745,13 +3740,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C75" s="4">
-        <v>142951</v>
+        <v>141655</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -3778,13 +3773,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C76" s="4">
-        <v>156399</v>
+        <v>141657</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
@@ -3810,12 +3805,14 @@
       <c r="A77" s="4">
         <v>73</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C77" s="4">
-        <v>157113</v>
+        <v>142753</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
@@ -3841,12 +3838,14 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C78" s="4">
-        <v>157118</v>
+        <v>142751</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
@@ -3872,12 +3871,14 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C79" s="4">
-        <v>157119</v>
+        <v>142951</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
@@ -3904,13 +3905,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C80" s="4">
-        <v>271322</v>
+        <v>156399</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
@@ -3936,14 +3937,12 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="B81" s="2"/>
       <c r="C81" s="4">
-        <v>311092</v>
+        <v>157113</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
@@ -3969,14 +3968,12 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="4">
-        <v>318586</v>
+        <v>157118</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="4">
         <v>0</v>
@@ -4004,10 +4001,10 @@
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="4">
-        <v>501294</v>
+        <v>157119</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -4034,13 +4031,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C84" s="4">
-        <v>127013</v>
+        <v>271322</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -4066,12 +4063,14 @@
       <c r="A85" s="4">
         <v>81</v>
       </c>
-      <c r="B85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C85" s="4">
-        <v>146328</v>
+        <v>311092</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
@@ -4097,12 +4096,14 @@
       <c r="A86" s="4">
         <v>82</v>
       </c>
-      <c r="B86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C86" s="4">
-        <v>146328</v>
+        <v>318586</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E86" s="4">
         <v>0</v>
@@ -4130,10 +4131,10 @@
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="4">
-        <v>146753</v>
+        <v>501294</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
@@ -4160,13 +4161,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C88" s="4">
-        <v>146754</v>
+        <v>127013</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4">
         <v>0</v>
@@ -4192,14 +4193,12 @@
       <c r="A89" s="4">
         <v>85</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="4">
-        <v>144082</v>
+        <v>146328</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4">
         <v>0</v>
@@ -4225,14 +4224,12 @@
       <c r="A90" s="4">
         <v>86</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="4">
-        <v>361275</v>
+        <v>146328</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E90" s="4">
         <v>0</v>
@@ -4255,11 +4252,19 @@
       <c r="U90" s="2"/>
     </row>
     <row r="91" spans="1:21">
-      <c r="A91" s="2"/>
+      <c r="A91" s="4">
+        <v>87</v>
+      </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="C91" s="4">
+        <v>146753</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4278,11 +4283,21 @@
       <c r="U91" s="2"/>
     </row>
     <row r="92" spans="1:21">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="A92" s="4">
+        <v>88</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" s="4">
+        <v>146754</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4301,11 +4316,21 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="A93" s="4">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="4">
+        <v>144082</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4324,11 +4349,21 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="A94" s="4">
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="4">
+        <v>361275</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4347,11 +4382,19 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="2"/>
+      <c r="A95" s="4">
+        <v>91</v>
+      </c>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="C95" s="4">
+        <v>558271</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -7221,6 +7264,98 @@
       <c r="T219" s="2"/>
       <c r="U219" s="2"/>
     </row>
+    <row r="220" spans="1:21">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="2"/>
+    </row>
+    <row r="221" spans="1:21">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="2"/>
+      <c r="U221" s="2"/>
+    </row>
+    <row r="222" spans="1:21">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="2"/>
+      <c r="U222" s="2"/>
+    </row>
+    <row r="223" spans="1:21">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="2"/>
+      <c r="U223" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/wolf/Excel/Effects_特效.xlsx
+++ b/wolf/Excel/Effects_特效.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>Int</t>
   </si>
@@ -1369,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U223"/>
+  <dimension ref="A1:U220"/>
   <sheetFormatPr defaultColWidth="12.0666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="12.0666666666667" style="1"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="4">
-        <v>687895</v>
+        <v>556585</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4">
-        <v>687897</v>
+        <v>674918</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4">
-        <v>687899</v>
+        <v>565350</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4">
-        <v>556585</v>
+        <v>567138</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4">
-        <v>674918</v>
+        <v>567139</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4">
-        <v>565350</v>
+        <v>525387</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="4">
-        <v>567138</v>
+        <v>501310</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -1743,12 +1743,14 @@
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C13" s="4">
-        <v>567139</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>57202</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1774,12 +1776,14 @@
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C14" s="4">
-        <v>525387</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>365194</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -1805,12 +1809,14 @@
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C15" s="4">
-        <v>501310</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>28451</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -1836,14 +1842,14 @@
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
+      <c r="B16" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C16" s="4">
-        <v>57202</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>12</v>
+        <v>526080</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1869,14 +1875,12 @@
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="4">
-        <v>365194</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>14</v>
+        <v>464265</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1902,14 +1906,12 @@
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B18" s="6"/>
       <c r="C18" s="4">
-        <v>28451</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>16</v>
+        <v>266517</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -1935,14 +1937,12 @@
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="6"/>
       <c r="C19" s="4">
-        <v>526080</v>
+        <v>266518</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="4">
-        <v>464265</v>
+        <v>266519</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="4">
-        <v>266517</v>
+        <v>266520</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="4">
-        <v>266518</v>
+        <v>266521</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
@@ -2063,10 +2063,10 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="4">
-        <v>266519</v>
+        <v>439411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2094,10 +2094,10 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="4">
-        <v>266520</v>
+        <v>484531</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2125,10 +2125,10 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="4">
-        <v>266521</v>
+        <v>144088</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2156,10 +2156,10 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="4">
-        <v>439411</v>
+        <v>439415</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2187,10 +2187,10 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="4">
-        <v>484531</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>144093</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2218,10 +2218,10 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="4">
-        <v>144088</v>
+        <v>326212</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2249,10 +2249,10 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="4">
-        <v>439415</v>
+        <v>326224</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2280,10 +2280,10 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="4">
-        <v>144093</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>21</v>
+        <v>383667</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="4">
-        <v>326212</v>
+        <v>383676</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>22</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="4">
-        <v>326224</v>
+        <v>386040</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>22</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="4">
-        <v>383667</v>
+        <v>394667</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="4">
-        <v>383676</v>
+        <v>394678</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>22</v>
@@ -2433,12 +2433,14 @@
       <c r="A35" s="4">
         <v>31</v>
       </c>
-      <c r="B35" s="6"/>
+      <c r="B35" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="C35" s="4">
-        <v>386040</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>22</v>
+        <v>220840</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -2460,16 +2462,16 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" ht="17.25" spans="1:21">
       <c r="A36" s="4">
         <v>32</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="4">
-        <v>394667</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>22</v>
+      <c r="B36" s="2"/>
+      <c r="C36" s="7">
+        <v>485354</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -2495,12 +2497,14 @@
       <c r="A37" s="4">
         <v>33</v>
       </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C37" s="4">
-        <v>394678</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>22</v>
+        <v>220841</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -2526,11 +2530,11 @@
       <c r="A38" s="4">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="4">
-        <v>220840</v>
+        <v>220842</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>24</v>
@@ -2555,16 +2559,18 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" ht="17.25" spans="1:21">
+    <row r="39" spans="1:21">
       <c r="A39" s="4">
         <v>35</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="7">
-        <v>485354</v>
+      <c r="B39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="4">
+        <v>220843</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -2594,7 +2600,7 @@
         <v>23</v>
       </c>
       <c r="C40" s="4">
-        <v>220841</v>
+        <v>220844</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>24</v>
@@ -2627,7 +2633,7 @@
         <v>23</v>
       </c>
       <c r="C41" s="4">
-        <v>220842</v>
+        <v>220845</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>24</v>
@@ -2660,7 +2666,7 @@
         <v>23</v>
       </c>
       <c r="C42" s="4">
-        <v>220843</v>
+        <v>220846</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>24</v>
@@ -2693,7 +2699,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="4">
-        <v>220844</v>
+        <v>220847</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>24</v>
@@ -2726,7 +2732,7 @@
         <v>23</v>
       </c>
       <c r="C44" s="4">
-        <v>220845</v>
+        <v>220848</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>24</v>
@@ -2759,7 +2765,7 @@
         <v>23</v>
       </c>
       <c r="C45" s="4">
-        <v>220846</v>
+        <v>220849</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>24</v>
@@ -2792,7 +2798,7 @@
         <v>23</v>
       </c>
       <c r="C46" s="4">
-        <v>220847</v>
+        <v>220850</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>24</v>
@@ -2825,7 +2831,7 @@
         <v>23</v>
       </c>
       <c r="C47" s="4">
-        <v>220848</v>
+        <v>220851</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>24</v>
@@ -2858,7 +2864,7 @@
         <v>23</v>
       </c>
       <c r="C48" s="4">
-        <v>220849</v>
+        <v>220041</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>24</v>
@@ -2891,7 +2897,7 @@
         <v>23</v>
       </c>
       <c r="C49" s="4">
-        <v>220850</v>
+        <v>220469</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>24</v>
@@ -2921,13 +2927,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C50" s="4">
-        <v>220851</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>24</v>
+        <v>31645</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -2953,14 +2959,14 @@
       <c r="A51" s="4">
         <v>47</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>23</v>
+      <c r="B51" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C51" s="4">
-        <v>220041</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>24</v>
+        <v>4366</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -2987,13 +2993,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C52" s="4">
-        <v>220469</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>24</v>
+        <v>4367</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3020,10 +3026,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C53" s="4">
-        <v>31645</v>
+        <v>4368</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -3052,14 +3058,12 @@
       <c r="A54" s="4">
         <v>50</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="4">
-        <v>4366</v>
+        <v>144084</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
@@ -3085,11 +3089,9 @@
       <c r="A55" s="4">
         <v>51</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="4">
-        <v>4367</v>
+        <v>146786</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -3118,14 +3120,12 @@
       <c r="A56" s="4">
         <v>52</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="4">
-        <v>4368</v>
+        <v>144083</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E56" s="4">
         <v>0</v>
@@ -3151,12 +3151,14 @@
       <c r="A57" s="4">
         <v>53</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C57" s="4">
-        <v>144084</v>
+        <v>32240</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
@@ -3182,9 +3184,11 @@
       <c r="A58" s="4">
         <v>54</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C58" s="4">
-        <v>146786</v>
+        <v>59956</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
@@ -3213,12 +3217,14 @@
       <c r="A59" s="4">
         <v>55</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C59" s="4">
-        <v>144083</v>
+        <v>73402</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
@@ -3245,10 +3251,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C60" s="4">
-        <v>32240</v>
+        <v>88762</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -3278,10 +3284,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C61" s="4">
-        <v>59956</v>
+        <v>88773</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -3311,10 +3317,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4">
-        <v>73402</v>
+        <v>89073</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -3344,10 +3350,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4">
-        <v>88762</v>
+        <v>89109</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -3377,10 +3383,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C64" s="4">
-        <v>88773</v>
+        <v>89111</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -3410,10 +3416,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" s="4">
-        <v>89073</v>
+        <v>89112</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -3443,10 +3449,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C66" s="4">
-        <v>89109</v>
+        <v>89122</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -3476,10 +3482,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C67" s="4">
-        <v>89111</v>
+        <v>113903</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -3509,10 +3515,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4">
-        <v>89112</v>
+        <v>113913</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -3542,10 +3548,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C69" s="4">
-        <v>89122</v>
+        <v>113907</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -3575,10 +3581,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C70" s="4">
-        <v>113903</v>
+        <v>119917</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -3608,10 +3614,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C71" s="4">
-        <v>113913</v>
+        <v>130776</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -3641,10 +3647,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C72" s="4">
-        <v>113907</v>
+        <v>141655</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -3674,10 +3680,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C73" s="4">
-        <v>119917</v>
+        <v>141657</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -3707,10 +3713,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C74" s="4">
-        <v>130776</v>
+        <v>142753</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -3740,10 +3746,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C75" s="4">
-        <v>141655</v>
+        <v>142751</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -3773,10 +3779,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C76" s="4">
-        <v>141657</v>
+        <v>142951</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -3806,10 +3812,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C77" s="4">
-        <v>142753</v>
+        <v>156399</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -3838,11 +3844,9 @@
       <c r="A78" s="4">
         <v>74</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="B78" s="2"/>
       <c r="C78" s="4">
-        <v>142751</v>
+        <v>157113</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -3871,11 +3875,9 @@
       <c r="A79" s="4">
         <v>75</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="4">
-        <v>142951</v>
+        <v>157118</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -3904,11 +3906,9 @@
       <c r="A80" s="4">
         <v>76</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="4">
-        <v>156399</v>
+        <v>157119</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -3937,9 +3937,11 @@
       <c r="A81" s="4">
         <v>77</v>
       </c>
-      <c r="B81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C81" s="4">
-        <v>157113</v>
+        <v>271322</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -3968,9 +3970,11 @@
       <c r="A82" s="4">
         <v>78</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C82" s="4">
-        <v>157118</v>
+        <v>311092</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -3999,9 +4003,11 @@
       <c r="A83" s="4">
         <v>79</v>
       </c>
-      <c r="B83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C83" s="4">
-        <v>157119</v>
+        <v>318586</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -4030,11 +4036,9 @@
       <c r="A84" s="4">
         <v>80</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="4">
-        <v>271322</v>
+        <v>501294</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -4064,10 +4068,10 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C85" s="4">
-        <v>311092</v>
+        <v>127013</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -4096,11 +4100,9 @@
       <c r="A86" s="4">
         <v>82</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="4">
-        <v>318586</v>
+        <v>146328</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -4131,7 +4133,7 @@
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="4">
-        <v>501294</v>
+        <v>146328</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -4160,11 +4162,9 @@
       <c r="A88" s="4">
         <v>84</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="4">
-        <v>127013</v>
+        <v>146753</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -4193,9 +4193,11 @@
       <c r="A89" s="4">
         <v>85</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C89" s="4">
-        <v>146328</v>
+        <v>146754</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -4224,9 +4226,11 @@
       <c r="A90" s="4">
         <v>86</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="C90" s="4">
-        <v>146328</v>
+        <v>144082</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -4255,9 +4259,11 @@
       <c r="A91" s="4">
         <v>87</v>
       </c>
-      <c r="B91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C91" s="4">
-        <v>146753</v>
+        <v>361275</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -4286,14 +4292,12 @@
       <c r="A92" s="4">
         <v>88</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="B92" s="2"/>
       <c r="C92" s="4">
-        <v>146754</v>
+        <v>558271</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E92" s="4">
         <v>0</v>
@@ -4316,21 +4320,11 @@
       <c r="U92" s="2"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="4">
-        <v>89</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C93" s="4">
-        <v>144082</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="4">
-        <v>0</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4349,21 +4343,11 @@
       <c r="U93" s="2"/>
     </row>
     <row r="94" spans="1:21">
-      <c r="A94" s="4">
-        <v>90</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C94" s="4">
-        <v>361275</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="4">
-        <v>0</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4382,19 +4366,11 @@
       <c r="U94" s="2"/>
     </row>
     <row r="95" spans="1:21">
-      <c r="A95" s="4">
-        <v>91</v>
-      </c>
+      <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="4">
-        <v>558271</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E95" s="4">
-        <v>0</v>
-      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -7287,75 +7263,6 @@
       <c r="T220" s="2"/>
       <c r="U220" s="2"/>
     </row>
-    <row r="221" spans="1:21">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
-      <c r="J221" s="2"/>
-      <c r="K221" s="2"/>
-      <c r="L221" s="2"/>
-      <c r="M221" s="2"/>
-      <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
-      <c r="P221" s="2"/>
-      <c r="Q221" s="2"/>
-      <c r="R221" s="2"/>
-      <c r="S221" s="2"/>
-      <c r="T221" s="2"/>
-      <c r="U221" s="2"/>
-    </row>
-    <row r="222" spans="1:21">
-      <c r="A222" s="2"/>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-      <c r="J222" s="2"/>
-      <c r="K222" s="2"/>
-      <c r="L222" s="2"/>
-      <c r="M222" s="2"/>
-      <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
-      <c r="P222" s="2"/>
-      <c r="Q222" s="2"/>
-      <c r="R222" s="2"/>
-      <c r="S222" s="2"/>
-      <c r="T222" s="2"/>
-      <c r="U222" s="2"/>
-    </row>
-    <row r="223" spans="1:21">
-      <c r="A223" s="2"/>
-      <c r="B223" s="2"/>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2"/>
-      <c r="M223" s="2"/>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
-      <c r="P223" s="2"/>
-      <c r="Q223" s="2"/>
-      <c r="R223" s="2"/>
-      <c r="S223" s="2"/>
-      <c r="T223" s="2"/>
-      <c r="U223" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
